--- a/Test Upload Excel Files/TestData-Director.xlsx
+++ b/Test Upload Excel Files/TestData-Director.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyleb\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Semicolon-TomorrowsVoice\Test Upload Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA85A02-06AD-40C0-B36B-759AC8EB43AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9795BB4C-824C-4BD5-86E5-9DCEDEB94425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8310" yWindow="3960" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -462,6 +462,7 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="66.28515625" customWidth="1"/>
   </cols>
   <sheetData>
